--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127338712</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vassjön, Vassjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>489054</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6825632</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127338968</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vassjön, Vassjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489263</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6825711</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127339043</v>
       </c>
       <c r="B2" t="n">
-        <v>79015</v>
+        <v>79019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127338712</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127338968</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127339043</v>
       </c>
       <c r="B2" t="n">
-        <v>79019</v>
+        <v>79021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127338712</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127338968</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127339043</v>
       </c>
       <c r="B2" t="n">
-        <v>79021</v>
+        <v>79024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127338712</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127338968</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127339043</v>
       </c>
       <c r="B2" t="n">
-        <v>79024</v>
+        <v>79030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127338712</v>
       </c>
       <c r="B3" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127338968</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin</t>
+          <t>Elis Lewin, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elis Lewin, Filippa Paperin</t>
+          <t>Filippa Paperin, Elis Lewin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127339043</v>
+        <v>127338968</v>
       </c>
       <c r="B2" t="n">
-        <v>79030</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489159</v>
+        <v>489263</v>
       </c>
       <c r="R2" t="n">
-        <v>6825781</v>
+        <v>6825711</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elis Lewin</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>127338712</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127338968</v>
+        <v>127339043</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489263</v>
+        <v>489159</v>
       </c>
       <c r="R4" t="n">
-        <v>6825711</v>
+        <v>6825781</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Filippa Paperin, Elis Lewin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 31740-2025 artfynd.xlsx
+++ b/artfynd/A 31740-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127338968</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127338712</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127339043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>